--- a/config/Vehicle_infor.xlsx
+++ b/config/Vehicle_infor.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anhta\INNOVA\000. WORKSPACE\001.___My_Python_Project\CreateSimualationfile\config\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC757FB-CF9C-4944-A2BE-ECE10664E743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6350"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VIN_YMME" sheetId="9" r:id="rId1"/>
     <sheet name="NWS" sheetId="4" r:id="rId2"/>
     <sheet name="PIDs" sheetId="3" r:id="rId3"/>
-    <sheet name="OBD2 DTC" sheetId="7" r:id="rId4"/>
-    <sheet name="OBD2 Freeze Frame" sheetId="8" r:id="rId5"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
-    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
     <definedName name="a">#REF!</definedName>
@@ -266,7 +270,7 @@
     <definedName name="xxx">'[3]9.Scan All System'!#REF!</definedName>
     <definedName name="xxxxx">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -284,7 +288,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
   <si>
     <t>VIN</t>
   </si>
@@ -358,41 +362,68 @@
     <t>HKMA_0240</t>
   </si>
   <si>
-    <t>B0010</t>
-  </si>
-  <si>
-    <t>B0001</t>
-  </si>
-  <si>
     <t>ItemID</t>
   </si>
   <si>
     <t>Value</t>
   </si>
   <si>
-    <t>eLDID_0001_Wheel speed sensor -Left Front_CAN_UDS_003</t>
-  </si>
-  <si>
-    <t>eLDID_0002_Wheel speed sensor -Right Front_CAN_UDS_003</t>
-  </si>
-  <si>
-    <t>eLDID_0003_Wheel speed sensor -Left Rear_CAN_UDS_003</t>
-  </si>
-  <si>
-    <t>eLDID_0004_Wheel speed sensor -Right Rear_CAN_UDS_003</t>
+    <t>ECM_ID_00001</t>
+  </si>
+  <si>
+    <t>ECM_ID_00002</t>
+  </si>
+  <si>
+    <t>ECM_ID_00003</t>
+  </si>
+  <si>
+    <t>ECM_ID_00004</t>
+  </si>
+  <si>
+    <t>ECM_ID_00005</t>
+  </si>
+  <si>
+    <t>ECM_ID_00019</t>
+  </si>
+  <si>
+    <t>ECM_ID_00020</t>
+  </si>
+  <si>
+    <t>ECM_ID_00031</t>
+  </si>
+  <si>
+    <t>ECM_ID_00032</t>
+  </si>
+  <si>
+    <t>ECM_ID_00033</t>
+  </si>
+  <si>
+    <t>ECM_ID_00034</t>
+  </si>
+  <si>
+    <t>ECM_ID_00035</t>
+  </si>
+  <si>
+    <t>MsgID/ECUID/ProfileID</t>
+  </si>
+  <si>
+    <t>HMA_00232</t>
+  </si>
+  <si>
+    <t>Value (HEX)</t>
+  </si>
+  <si>
+    <t>B001000</t>
+  </si>
+  <si>
+    <t>B000100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,154 +443,15 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="0"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -578,194 +470,8 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -786,256 +492,26 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1047,67 +523,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.14996795556505021"/>
+      </font>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -1123,14 +581,11 @@
       <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
+        <patternFill patternType="none"/>
       </fill>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1138,12 +593,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="VW_NonUDSFormular"/>
@@ -1158,7 +616,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Hictorical"/>
@@ -1195,7 +653,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="History of file"/>
@@ -1332,7 +790,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="History of file"/>
@@ -1361,11 +819,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table634" displayName="Table634" ref="A1:B5" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B5" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="2">
-    <tableColumn id="26" name="ItemID" dataDxfId="0"/>
-    <tableColumn id="1" name="Value" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table634" displayName="Table634" ref="C1:E13" totalsRowShown="0">
+  <autoFilter ref="C1:E13" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <tableColumns count="3">
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="ItemID" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Value" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{966D4AA6-1CB8-4F98-AD91-3A99D6FB0602}" name="Value (HEX)" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1623,25 +1082,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.7272727272727" customWidth="1"/>
-    <col min="2" max="2" width="5.90909090909091" customWidth="1"/>
-    <col min="3" max="3" width="13.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="8.63636363636364" customWidth="1"/>
+    <col min="1" max="1" width="24.77734375" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="10.5454545454545" customWidth="1"/>
-    <col min="7" max="7" width="24.7272727272727" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" customWidth="1"/>
+    <col min="7" max="7" width="24.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1662,40 +1121,38 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="6">
         <v>2017</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="8"/>
+      <c r="G2" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="6" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="6.63636363636364" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1776,7 +1233,7 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -1790,7 +1247,7 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D7">
         <v>20</v>
@@ -1798,104 +1255,238 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9.10909090909091" defaultRowHeight="14.5" outlineLevelRow="4" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="64" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.7818181818182" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="9.10909090909091" style="3"/>
+    <col min="1" max="1" width="9.109375" style="2"/>
+    <col min="2" max="2" width="21" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.77734375" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D2" s="4">
+        <v>0.37</v>
+      </c>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:2">
-      <c r="A2" s="5" t="s">
+      <c r="D3" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="5" t="s">
+      <c r="D4" s="4">
+        <v>-0.94</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="7">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="5" t="s">
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="5" t="s">
+      <c r="D6" s="4">
+        <v>-0.82</v>
+      </c>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="7">
-        <v>23</v>
-      </c>
+      <c r="D7" s="4">
+        <v>-25.96</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="4">
+        <v>80.38</v>
+      </c>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4">
+        <v>-20.78</v>
+      </c>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="4">
+        <v>61.89</v>
+      </c>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="4">
+        <v>17.72</v>
+      </c>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="4">
+        <v>54.39</v>
+      </c>
+      <c r="E13" s="4"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A5">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="B2:B13">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"N/A"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
+  <conditionalFormatting sqref="C14:C1048576 C1">
+    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:A1048576 A1">
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+  <conditionalFormatting sqref="C14:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>